--- a/ConfigTools/Config/Datas/__tables__.xlsx
+++ b/ConfigTools/Config/Datas/__tables__.xlsx
@@ -1032,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="28.5833333333333" customWidth="1" style="4" min="2" max="2"/>
@@ -1463,6 +1463,66 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>TbMapBigLevel</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>MapBigLevelDef</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>MapBigLevel@MapLevelInfo.xlsx</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>BigLevelId</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>冒险大关</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>TbMapLevel</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>MapLevelDef</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>MapLevel@MapLevelInfo.xlsx</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>BigLevelId+LevelId</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>冒险小关</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" tooltip="mailto:Sheet3@AbilitySetting.xlsx" display="怪物@Monster.xlsx" r:id="rId1"/>

--- a/ConfigTools/Config/Datas/__tables__.xlsx
+++ b/ConfigTools/Config/Datas/__tables__.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="18350" windowHeight="6880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1227,6 +1227,11 @@
           <t>MonsterId</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
     </row>
     <row r="5" s="4">
       <c r="B5" s="0" t="inlineStr">
@@ -1250,6 +1255,11 @@
       <c r="F5" s="0" t="inlineStr">
         <is>
           <t>TowerId</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
@@ -1290,6 +1300,11 @@
           <t>BulletId</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="n"/>
@@ -1316,6 +1331,11 @@
           <t>BuffId</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n"/>
@@ -1342,6 +1362,11 @@
           <t>ItemTypeId</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="inlineStr">
@@ -1367,6 +1392,11 @@
           <t>EffectId</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
           <t>肉鸽效果</t>
@@ -1397,6 +1427,11 @@
           <t>ItemId</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
           <t>肉鸽商店道具</t>
@@ -1427,6 +1462,11 @@
           <t>PoolId</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
           <t>肉鸽商店池</t>
@@ -1457,6 +1497,11 @@
           <t>BigLevelId+LevelId</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
           <t>肉鸽小关</t>
@@ -1487,6 +1532,11 @@
           <t>BigLevelId</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
           <t>冒险大关</t>
@@ -1515,6 +1565,11 @@
       <c r="F18" s="0" t="inlineStr">
         <is>
           <t>BigLevelId+LevelId</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
